--- a/database/template-import-export/templates/template-kelembagaan.xlsx
+++ b/database/template-import-export/templates/template-kelembagaan.xlsx
@@ -26,7 +26,7 @@
     <t>Kelompok tani &amp; kelompok tani hutan per desa per tahun (ST2023 basis).</t>
   </si>
   <si>
-    <t>Dibuat otomatis: 22/9/2026, 14.21.33</t>
+    <t>Dibuat otomatis: 29/9/2026, 15.29.43</t>
   </si>
   <si>
     <t>CARA PAKAI</t>
